--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -57,8 +71,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>质检通知数量</t>
+      <t>报废数量</t>
     </r>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -679,9 +696,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1030,24 +1052,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:2">
+    <row r="1" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>1</formula1>
       <formula2>10000000</formula2>
     </dataValidation>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
@@ -29,7 +29,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报废人</t>
+    </r>
+  </si>
   <si>
     <r>
       <rPr>
@@ -66,6 +88,27 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用方</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -75,7 +118,7 @@
     </r>
   </si>
   <si>
-    <t>备注</t>
+    <t>明细备注</t>
   </si>
 </sst>
 </file>
@@ -88,7 +131,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +288,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -698,10 +747,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1052,31 +1101,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>1</formula1>
-      <formula2>10000000</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
@@ -745,12 +745,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1103,21 +1107,24 @@
   <sheetPr/>
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="5" width="9" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleScrapDetailTemplate.xlsx
@@ -29,29 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>报废人</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
       <rPr>
@@ -1105,13 +1083,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="5" width="9" style="2"/>
+    <col min="1" max="4" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1121,11 +1099,8 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
